--- a/FunctionalRequirements.xlsx
+++ b/FunctionalRequirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANN ELZA JOSE\Documents\Data Engineer\LMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85287206-DA4A-403B-B34F-262E5BD1F25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8379CFD-240F-40A9-AC13-871D281874D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2499A000-EA71-4847-80BE-7E359E955F9E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>Slno.</t>
   </si>
@@ -84,13 +84,19 @@
   </si>
   <si>
     <t>Update basic profile information like name, email, and password.</t>
+  </si>
+  <si>
+    <t>Data Modeling</t>
+  </si>
+  <si>
+    <t>popular courses among enrolled students</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +107,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -130,7 +144,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -467,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{156BACC6-17CB-499F-81E5-BD6C1099E290}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -597,6 +611,14 @@
         <v>14</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C2"/>
